--- a/02-Execucao/03-Execucao_Procedimentos/mapa-verificacao-achados.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/mapa-verificacao-achados.xlsx
@@ -13,7 +13,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variáveis Temporárias" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fontes de Informação'!$A$3:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Procedimentos de Auditoria'!$A$3:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ações de Verificação'!$A$3:$P$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Variáveis Temporárias'!$A$3:$E$8</definedName>
@@ -371,90 +370,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-    <col width="72" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="56" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="72" customWidth="1" min="16" max="16"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="n"/>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>filepath</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>chave_jurisdicionado</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>questionario</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>questionario</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Questionário eletrônico iGovTI</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>20260607-respostas-questionario.xlsx</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20260621-respostas-questionario.xlsx</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>firstname</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D4"/>
-  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 

--- a/02-Execucao/03-Execucao_Procedimentos/mapa-verificacao-achados.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/mapa-verificacao-achados.xlsx
@@ -373,21 +373,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A3:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -423,12 +411,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260621-respostas-questionario.xlsx</t>
+          <t>20260621-respostas-questionario-pos-avaliacao-evidencias.xlsx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>firstname</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ajustes de respostas decorrentes da avaliação de evidências</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>20260621-ajustes-evidencias-para-auditoria.xlsx</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Auditado</t>
         </is>
       </c>
     </row>
@@ -517,7 +527,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>(AV01 | (AV02 &amp; (AV03 | AV04)) | (AV05 &amp; AV06))</t>
+          <t>(AV01 | (AV02 &amp; (AV03 | (AV04 | AV84))) | (AV05 &amp; AV06))</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -542,7 +552,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>((AV07 | AV08 | AV09 | AV10) | AV11 | (AV12 &amp; AV13))</t>
+          <t>(((AV07 | AV85) | (AV08 | AV86) | (AV09 | AV87) | (AV10 | AV88)) | (AV11 | AV89) | ((AV12 | AV90) &amp; (AV13 | AV91)))</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -567,7 +577,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>((AV14 | AV15 | AV16 | AV17) | AV18 | AV19 | (AV20 | AV21 | AV22 | AV23) | AV24)</t>
+          <t>(((AV14 | AV92) | (AV15 | AV93) | (AV16 | AV94) | (AV17 | AV95)) | (AV18 | AV96) | (AV19 | AV97) | ((AV20 | AV98) | (AV21 | AV99) | (AV22 | AV100) | AV23) | (AV24 | AV101))</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -592,7 +602,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>(((AV25 &amp; AV26) | AV27) | (AV28 | AV29) | ((AV30 &amp; AV31) | (AV32 &amp; AV33)) | ((AV34 | AV35) | (AV36 | AV37) | AV38) | (AV39 | AV40 | AV41 | AV42 | AV43 | AV44) | ((AV45 &amp; (AV46 | ((AV47 | AV48) &amp; (AV49 | AV50)) | (AV51 | AV52))) | (AV53 &amp; (AV49 | AV50 | AV51 | AV52))))</t>
+          <t>(((AV25 &amp; AV26) | AV27) | ((AV28 | AV102) | (AV29 | AV103)) | (((AV30 | AV104) &amp; (AV31 | AV105)) | ((AV32 | AV106) &amp; (AV33 | AV107))) | (((AV34 | AV108) | (AV35 | AV109)) | ((AV36 | AV110) | (AV37 | AV111)) | (AV38 | AV112)) | ((AV39 | AV113) | (AV40 | AV114) | (AV41 | AV115) | (AV42 | AV116) | (AV43 | AV117) | (AV44 | AV118)) | ((AV45 &amp; (AV46 | (((AV47 | AV119) | (AV48 | AV120)) &amp; ((AV49 | AV121) | (AV50 | AV122))) | ((AV51 | AV123) | AV52))) | (AV53 &amp; ((AV49 | AV121) | (AV50 | AV122) | (AV51 | AV123) | AV52))))</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -617,7 +627,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>((AV54 | AV55 | AV56) | (AV57 | AV58) | (AV59 | AV60 | AV61 | AV62 | AV63) | (AV64 | AV65 | AV66) | (AV67 | AV68 | AV69 | AV70 | AV71 | AV72))</t>
+          <t>(((AV54 | AV124) | (AV55 | AV125) | (AV56 | AV126)) | ((AV57 | AV127) | (AV58 | AV128)) | ((AV59 | AV129) | (AV60 | AV130) | (AV61 | AV131) | (AV62 | AV132) | (AV63 | AV133)) | ((AV64 | AV134) | (AV65 | AV135) | (AV66 | AV136)) | ((AV67 | AV137) | (AV68 | AV138) | (AV69 | AV139) | (AV70 | AV140) | (AV71 | AV141) | (AV72 | AV142)))</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -642,7 +652,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>((AV73 | AV74 | AV75 | AV76 | AV77) | AV78 | (AV79 | AV80 | AV81 | AV82) | AV83)</t>
+          <t>(((AV73 | AV143) | (AV74 | AV144) | (AV75 | AV145) | (AV76 | AV146) | (AV77 | AV147)) | (AV78 | AV148) | ((AV79 | AV149) | (AV80 | AV150) | (AV81 | AV151) | AV82) | AV83)</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -668,7 +678,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5477,6 +5487,3317 @@
       <c r="P86" s="3" t="inlineStr">
         <is>
           <t>designe formalmente equipe responsável pelo planejamento das contratações de TIC, atentando-se, minimamente, em assegurar a participação da área requisitante, da área técnica de TIC e das demais áreas necessárias, com definição das responsabilidades de seus integrantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AV84</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>q0103[D]</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TI.
+COBIT 2019, APO01.09 - Definição e comunicação de políticas e procedimentos: estabelecer e comunicar políticas e procedimentos de gestão de TI que orientem papéis, responsabilidades e controles.
+ABNT NBR ISO/IEC 38500:2025, item 5.6.1 - Governança efetiva de TI: responsabilização clara, estrutura adequada de tomada de decisão e direção organizacional compatível com o uso atual e futuro da tecnologia.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que a área de TI possui atribuições formalizadas relacionadas à governança, planejamento ou gestão de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Área de TIC sem atribuições formais suficientes para planejamento, coordenação, gestão, execução, monitoramento e controle da TIC.</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>defina formalmente as atribuições da área de TIC, atentando-se, minimamente, em abranger as atividades de planejamento, coordenação, gestão, execução, monitoramento e controle da TIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AV85</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>q1001ext[C]</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>COBIT 2019, EDM01.02 - Dirigir o sistema de governança: orientar estruturas, princípios, processos e práticas de governança para assegurar que a TI apoie os objetivos organizacionais.
+COBIT 2019, MEA01.04 - Avaliar o desempenho: monitorar e avaliar periodicamente o desempenho e a conformidade da TI em relação a objetivos, indicadores, metas e expectativas das partes interessadas.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.1: necessidade de estrutura de governança de TI, especialmente Comitê de Tecnologia da Informação ou instância equivalente, com participação de áreas relevantes, responsabilidade de alinhar as ações de TI aos objetivos institucionais, priorizar investimentos e monitorar o desempenho da TI com base em indicadores e metas.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que define os papéis e responsabilidades da área de gestão de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Ausência ou insuficiência de modelo básico de governança e gestão de TIC com papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>estabeleça modelo básico de governança e gestão de TIC, atentando-se, minimamente, em definir papéis e responsabilidades, objetivos, indicadores, metas e forma de acompanhamento periódico do desempenho da TIC pela alta administração</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AV86</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>q1001ext[H]</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>COBIT 2019, EDM01.02 - Dirigir o sistema de governança: orientar estruturas, princípios, processos e práticas de governança para assegurar que a TI apoie os objetivos organizacionais.
+COBIT 2019, MEA01.04 - Avaliar o desempenho: monitorar e avaliar periodicamente o desempenho e a conformidade da TI em relação a objetivos, indicadores, metas e expectativas das partes interessadas.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.1: necessidade de estrutura de governança de TI, especialmente Comitê de Tecnologia da Informação ou instância equivalente, com participação de áreas relevantes, responsabilidade de alinhar as ações de TI aos objetivos institucionais, priorizar investimentos e monitorar o desempenho da TI com base em indicadores e metas.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que estabeleceu objetivos, indicadores e metas para a gestão de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Ausência ou insuficiência de modelo básico de governança e gestão de TIC com papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>estabeleça modelo básico de governança e gestão de TIC, atentando-se, minimamente, em definir papéis e responsabilidades, objetivos, indicadores, metas e forma de acompanhamento periódico do desempenho da TIC pela alta administração</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AV87</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>q1002ext[A]</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>COBIT 2019, EDM01.02 - Dirigir o sistema de governança: orientar estruturas, princípios, processos e práticas de governança para assegurar que a TI apoie os objetivos organizacionais.
+COBIT 2019, MEA01.04 - Avaliar o desempenho: monitorar e avaliar periodicamente o desempenho e a conformidade da TI em relação a objetivos, indicadores, metas e expectativas das partes interessadas.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.1: necessidade de estrutura de governança de TI, especialmente Comitê de Tecnologia da Informação ou instância equivalente, com participação de áreas relevantes, responsabilidade de alinhar as ações de TI aos objetivos institucionais, priorizar investimentos e monitorar o desempenho da TI com base em indicadores e metas.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que rotinas de monitoramento do desempenho da gestão de tecnologia da informação estão definidas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Ausência ou insuficiência de modelo básico de governança e gestão de TIC com papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>estabeleça modelo básico de governança e gestão de TIC, atentando-se, minimamente, em definir papéis e responsabilidades, objetivos, indicadores, metas e forma de acompanhamento periódico do desempenho da TIC pela alta administração</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AV88</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>q1002ext[C]</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>COBIT 2019, EDM01.02 - Dirigir o sistema de governança: orientar estruturas, princípios, processos e práticas de governança para assegurar que a TI apoie os objetivos organizacionais.
+COBIT 2019, MEA01.04 - Avaliar o desempenho: monitorar e avaliar periodicamente o desempenho e a conformidade da TI em relação a objetivos, indicadores, metas e expectativas das partes interessadas.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.1: necessidade de estrutura de governança de TI, especialmente Comitê de Tecnologia da Informação ou instância equivalente, com participação de áreas relevantes, responsabilidade de alinhar as ações de TI aos objetivos institucionais, priorizar investimentos e monitorar o desempenho da TI com base em indicadores e metas.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que os indicadores de desempenho da gestão de tecnologia da informação estão implantados (há coleta e análise dos dados necessários à medição de desempenho). Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ausência ou insuficiência de modelo básico de governança e gestão de TIC com papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>estabeleça modelo básico de governança e gestão de TIC, atentando-se, minimamente, em definir papéis e responsabilidades, objetivos, indicadores, metas e forma de acompanhamento periódico do desempenho da TIC pela alta administração</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AV89</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>q1001ext[E]</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Decreto nº 12.198/2024, art. 5º - Instituição do CGD, colegiado responsável por definir diretrizes e estratégias sobre uso de recursos digitais nos órgãos e entidades da administração pública federal direta, autárquica e fundacional.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.1: necessidade de estrutura de governança de TI, especialmente Comitê de Tecnologia da Informação ou instância equivalente, com participação de áreas relevantes, responsabilidade de alinhar as ações de TI aos objetivos institucionais, priorizar investimentos e monitorar o desempenho da TI com base em indicadores e metas.
+COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TI.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que dispõe de comitê de tecnologia da informação composto por representantes de áreas relevantes da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente não instituído formalmente.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>institua formalmente Comitê de TIC ou instância equivalente, atentando-se, minimamente, em definir sua composição, competências, periodicidade de reuniões, forma de registro das deliberações e acompanhamento dos encaminhamentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AV90</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>q1001ext[E]</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>COBIT 2019, MEA01.04 - Avaliar o desempenho: monitorar e avaliar periodicamente o desempenho e a conformidade da TI em relação a objetivos, indicadores, metas e expectativas das partes interessadas.
+Decreto nº 12.198/2024, art. 5º - Instituição do CGD, colegiado responsável por definir diretrizes e estratégias sobre uso de recursos digitais nos órgãos e entidades da administração pública federal direta, autárquica e fundacional.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.1: necessidade de estrutura de governança de TI, especialmente Comitê de Tecnologia da Informação ou instância equivalente, com participação de áreas relevantes, responsabilidade de alinhar as ações de TI aos objetivos institucionais, priorizar investimentos e monitorar o desempenho da TI com base em indicadores e metas.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que dispõe de comitê de tecnologia da informação composto por representantes de áreas relevantes da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, atentando-se, minimamente, em realizar reuniões periódicas, registrar atas, deliberações e encaminhamentos e acompanhar as decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AV91</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>q1001ext[F]</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>COBIT 2019, MEA01.04 - Avaliar o desempenho: monitorar e avaliar periodicamente o desempenho e a conformidade da TI em relação a objetivos, indicadores, metas e expectativas das partes interessadas.
+Decreto nº 12.198/2024, art. 5º - Instituição do CGD, colegiado responsável por definir diretrizes e estratégias sobre uso de recursos digitais nos órgãos e entidades da administração pública federal direta, autárquica e fundacional.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.1: necessidade de estrutura de governança de TI, especialmente Comitê de Tecnologia da Informação ou instância equivalente, com participação de áreas relevantes, responsabilidade de alinhar as ações de TI aos objetivos institucionais, priorizar investimentos e monitorar o desempenho da TI com base em indicadores e metas.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o comitê de tecnologia da informação realiza as atividades previstas em ato constitutivo. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, atentando-se, minimamente, em realizar reuniões periódicas, registrar atas, deliberações e encaminhamentos e acompanhar as decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AV92</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>q2101ext[A]</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO02.05 - Definir o plano e o roteiro estratégico: estabelecer plano e roteiro de TIC que traduzam a estratégia em iniciativas, prioridades, recursos, dependências, prazos e benefícios esperados.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as áreas demandantes de soluções de TI participam do processo de planejamento de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AV93</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>q2101ext[B]</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO02.05 - Definir o plano e o roteiro estratégico: estabelecer plano e roteiro de TIC que traduzam a estratégia em iniciativas, prioridades, recursos, dependências, prazos e benefícios esperados.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que estabeleceu critérios para orientar a seleção e a priorização das iniciativas de TI (projetos e ações) e os mantêm atualizados. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AV94</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>q2101ext[C]</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO02.05 - Definir o plano e o roteiro estratégico: estabelecer plano e roteiro de TIC que traduzam a estratégia em iniciativas, prioridades, recursos, dependências, prazos e benefícios esperados.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as análises de benefícios, de custos e de riscos subsidiam as decisões relacionadas à seleção e à priorização das iniciativas de TI (projetos e ações). Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AV95</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>q2101ext[D]</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO02.05 - Definir o plano e o roteiro estratégico: estabelecer plano e roteiro de TIC que traduzam a estratégia em iniciativas, prioridades, recursos, dependências, prazos e benefícios esperados.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de planejamento de TI está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades). Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AV96</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>q2102ext[A]</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO02.05 - Definir o plano e o roteiro estratégico: estabelecer plano e roteiro de TIC que traduzam a estratégia em iniciativas, prioridades, recursos, dependências, prazos e benefícios esperados.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Ausência de aprovação formal do plano de TIC.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>submeta o plano de TIC à aprovação formal do dirigente máximo ou de dirigente ou colegiado integrante da alta administração, mantendo registro do respectivo ato de aprovação</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AV97</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>q2102ext[D]</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO02.05 - Definir o plano e o roteiro estratégico: estabelecer plano e roteiro de TIC que traduzam a estratégia em iniciativas, prioridades, recursos, dependências, prazos e benefícios esperados.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as iniciativas de TI (projetos e ações) constantes do plano de TI alinham-se aos objetivos e iniciativas definidos no planejamento institucional (como PPA, planos estratégicos, planos setoriais e plano de governo, no caso de municípios), bem como, quando aplicável, às estratégias e diretrizes estabelecidas por instâncias superiores de governança (como a Estratégia Nacional de Tecnologia da Informação e Comunicação do Poder Judiciário - ENTIC-JUD, normas e orientações do SETIC/PRODERJ (para órgãos estaduais) ou instâncias de governança equivalentes no âmbito municipal). Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem alinhamento adequado ao planejamento institucional.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>revise o plano de TIC para explicitar seu alinhamento ao planejamento institucional, às diretrizes superiores e às necessidades das áreas finalísticas e administrativas, relacionando objetivos, iniciativas, indicadores e metas de TIC aos resultados institucionais pretendidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AV98</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>q2102ext[C]</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO06.03 - Criar e manter orçamentos: elaborar e manter orçamento de TIC alinhado ao portfólio, ao planejamento e às prioridades aprovadas.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o plano de TI fundamenta a proposta orçamentária da área de TI e o plano de contratações. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem integração adequada com orçamento, plano de contratações, projetos ou contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>integre o plano de TIC à proposta orçamentária, ao plano de contratações e às contratações de TIC, atentando-se, minimamente, em priorizar as demandas conforme sua relevância, seus riscos e a capacidade de execução da organização</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AV99</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>q2802ext[C]</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO06.03 - Criar e manter orçamentos: elaborar e manter orçamento de TIC alinhado ao portfólio, ao planejamento e às prioridades aprovadas.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que na elaboração do PCA são considerados os demais instrumentos de planejamento da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem integração adequada com orçamento, plano de contratações, projetos ou contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>integre o plano de TIC à proposta orçamentária, ao plano de contratações e às contratações de TIC, atentando-se, minimamente, em priorizar as demandas conforme sua relevância, seus riscos e a capacidade de execução da organização</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AV100</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>q2802ext[D]</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO06.03 - Criar e manter orçamentos: elaborar e manter orçamento de TIC alinhado ao portfólio, ao planejamento e às prioridades aprovadas.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o PCA fundamenta a proposta orçamentária da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem integração adequada com orçamento, plano de contratações, projetos ou contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>integre o plano de TIC à proposta orçamentária, ao plano de contratações e às contratações de TIC, atentando-se, minimamente, em priorizar as demandas conforme sua relevância, seus riscos e a capacidade de execução da organização</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AV101</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>q2102ext[E]</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO02.05 - Definir o plano e o roteiro estratégico: estabelecer plano e roteiro de TIC que traduzam a estratégia em iniciativas, prioridades, recursos, dependências, prazos e benefícios esperados.
+Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4: necessidade de instituir formalmente plano diretor de TI, contemplando desdobramento de diretrizes estratégicas, vinculação das ações de TI a indicadores e metas de negócio, vinculação das ações de TI a indicadores e metas de serviços ao cidadão e vinculação das ações priorizadas ao orçamento de TI.
+Acórdão TCE-RJ 44.490/2024-PLEN, item II.3 e subitens II.3.1 a II.3.5: necessidade de estabelecer processo estruturado, com participação de representantes das principais secretarias, para elaborar, manter e revisar periodicamente o PDTI, contemplando objetivos, indicadores e metas de TI alinhados aos objetivos de negócio, riscos que possam impactar objetivos e metas, projetos, aquisições e ações necessárias, alocação de recursos e ações de divulgação e monitoramento do PDTI após aprovação pela autoridade máxima.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que é feito acompanhamento concomitante à execução do plano de TI, com vistas a assegurar sua observância e possibilitar a realização de ajustes que se fizerem necessário. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Ausência de acompanhamento, revisão ou atualização periódica do plano de TIC.</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>estabeleça e execute rotina periódica de acompanhamento, revisão e atualização do plano de TIC, atentando-se, minimamente, em registrar a execução das iniciativas, as pendências, as reprogramações e as deliberações adotadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AV102</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>q2703ext[B]</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.01 - Adquirir e manter pessoal adequado e apropriado: assegurar quantidade e perfil de profissionais compatíveis com as necessidades de TIC.
+COBIT 2019, APO07.05 - Planejar e monitorar o uso de recursos humanos de TI e de negócio: planejar, alocar e acompanhar capacidade de pessoal para iniciativas, operações e serviços de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que definiu-se o quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação com base em critério(s) ou procedimento(s) técnico(s). Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>A organização não definiu o quantitativo necessário de pessoal de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>estime e mantenha atualizado o quantitativo necessário de pessoal de TIC e segurança da informação, considerando o porte e a complexidade da organização, os serviços críticos, os sistemas mantidos, as contratações vigentes e os riscos relevantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AV103</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>q2703ext[C]</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.01 - Adquirir e manter pessoal adequado e apropriado: assegurar quantidade e perfil de profissionais compatíveis com as necessidades de TIC.
+COBIT 2019, APO07.05 - Planejar e monitorar o uso de recursos humanos de TI e de negócio: planejar, alocar e acompanhar capacidade de pessoal para iniciativas, operações e serviços de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que definiu-se, de maneira documentada, um quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>A organização não definiu o quantitativo necessário de pessoal de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>estime e mantenha atualizado o quantitativo necessário de pessoal de TIC e segurança da informação, considerando o porte e a complexidade da organização, os serviços críticos, os sistemas mantidos, as contratações vigentes e os riscos relevantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AV104</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>q2708[A]</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TIC.
+COBIT 2019, APO07.01 - Adquirir e manter pessoal adequado e apropriado: assegurar quantidade e perfil de profissionais compatíveis com as necessidades de TIC.
+COBIT 2019, APO07.02 - Identificar pessoal-chave de TI: identificar funções e pessoas críticas para reduzir dependência individual, perda de conhecimento e descontinuidade.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que possui em sua estrutura cargos efetivos em tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>avalie a necessidade de instituir cargos, funções, gratificações, perfis ou ocupações específicas de TIC e segurança da informação e adote a solução compatível com as necessidades institucionais e a capacidade administrativa da organização</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AV105</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>q2708[B]</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TIC.
+COBIT 2019, APO07.01 - Adquirir e manter pessoal adequado e apropriado: assegurar quantidade e perfil de profissionais compatíveis com as necessidades de TIC.
+COBIT 2019, APO07.02 - Identificar pessoal-chave de TI: identificar funções e pessoas críticas para reduzir dependência individual, perda de conhecimento e descontinuidade.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que possui em sua estrutura cargos ou funções formalmente atribuídas à área de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>avalie a necessidade de instituir cargos, funções, gratificações, perfis ou ocupações específicas de TIC e segurança da informação e adote a solução compatível com as necessidades institucionais e a capacidade administrativa da organização</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AV106</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>q2708[C]</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TIC.
+COBIT 2019, APO07.01 - Adquirir e manter pessoal adequado e apropriado: assegurar quantidade e perfil de profissionais compatíveis com as necessidades de TIC.
+COBIT 2019, APO07.02 - Identificar pessoal-chave de TI: identificar funções e pessoas críticas para reduzir dependência individual, perda de conhecimento e descontinuidade.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que possui em sua estrutura cargos efetivos em segurança da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>avalie a necessidade de instituir cargos, funções, gratificações, perfis ou ocupações específicas de TIC e segurança da informação e adote a solução compatível com as necessidades institucionais e a capacidade administrativa da organização</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AV107</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>q2708[D]</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TIC.
+COBIT 2019, APO07.01 - Adquirir e manter pessoal adequado e apropriado: assegurar quantidade e perfil de profissionais compatíveis com as necessidades de TIC.
+COBIT 2019, APO07.02 - Identificar pessoal-chave de TI: identificar funções e pessoas críticas para reduzir dependência individual, perda de conhecimento e descontinuidade.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que possui em sua estrutura cargos ou funções formalmente atribuídas à área de segurança da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>avalie a necessidade de instituir cargos, funções, gratificações, perfis ou ocupações específicas de TIC e segurança da informação e adote a solução compatível com as necessidades institucionais e a capacidade administrativa da organização</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AV108</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>q2701ext[A]</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TIC.
+COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as responsabilidades e atribuições dos gestores da área de tecnologia da informação estão definidas, documentadas e publicadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>defina perfis profissionais mínimos para gestores e colaboradores de TIC e segurança da informação, atentando-se, minimamente, em estabelecer conhecimentos, habilidades, experiência e responsabilidades requeridos e utilizar esses perfis na seleção e designação dos responsáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AV109</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>q2701ext[C]</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TIC.
+COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que relacionou-se, no perfil profissional, além de requerimentos de ordem legal, um conjunto de competências e habilidades que os ocupantes dos cargos de gestão devem possuir. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>defina perfis profissionais mínimos para gestores e colaboradores de TIC e segurança da informação, atentando-se, minimamente, em estabelecer conhecimentos, habilidades, experiência e responsabilidades requeridos e utilizar esses perfis na seleção e designação dos responsáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AV110</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>q2702ext[A]</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TIC.
+COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as responsabilidades e atribuições das ocupações ou grupo de ocupações da área de tecnologia da informação estão definidas, documentadas e publicadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>defina perfis profissionais mínimos para gestores e colaboradores de TIC e segurança da informação, atentando-se, minimamente, em estabelecer conhecimentos, habilidades, experiência e responsabilidades requeridos e utilizar esses perfis na seleção e designação dos responsáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>AV111</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>q2702ext[C]</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TIC.
+COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que relacionou-se, no perfil profissional, além de requerimentos de ordem legal, um conjunto de competências e habilidades que os ocupantes dos cargos devem possuir. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>defina perfis profissionais mínimos para gestores e colaboradores de TIC e segurança da informação, atentando-se, minimamente, em estabelecer conhecimentos, habilidades, experiência e responsabilidades requeridos e utilizar esses perfis na seleção e designação dos responsáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AV112</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>q2704ext[B]</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir, comunicar e manter papéis e responsabilidades relacionados à governança e gestão de TIC.
+COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que os gestores são selecionados com base em perfil profissional previamente definido e documentado, e compatível com o cargo ou função para o qual tenha sido indicado. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>defina perfis profissionais mínimos para gestores e colaboradores de TIC e segurança da informação, atentando-se, minimamente, em estabelecer conhecimentos, habilidades, experiência e responsabilidades requeridos e utilizar esses perfis na seleção e designação dos responsáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>AV113</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>q2705ext[B]</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.
+ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3: definir papéis e responsabilidades de segurança da informação e promover conscientização, educação e treinamento em segurança.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as lacunas de competências de liderança e gestão necessárias para a atuação dos gestores da organização são identificadas e documentadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>realize diagnóstico periódico das lacunas de competências dos gestores e colaboradores de TIC e segurança da informação e estabeleça plano de tratamento, contemplando, conforme a necessidade, capacitação, realocação, provimento, apoio especializado, compartilhamento de estrutura ou contratação com transferência de conhecimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AV114</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>q2705ext[C]</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.
+ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3: definir papéis e responsabilidades de segurança da informação e promover conscientização, educação e treinamento em segurança.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as lacunas de competências técnicas da área de tecnologia da informação necessárias para a atuação dos colaboradores da organização são identificadas e documentadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>realize diagnóstico periódico das lacunas de competências dos gestores e colaboradores de TIC e segurança da informação e estabeleça plano de tratamento, contemplando, conforme a necessidade, capacitação, realocação, provimento, apoio especializado, compartilhamento de estrutura ou contratação com transferência de conhecimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>AV115</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>q2705ext[D]</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.
+ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3: definir papéis e responsabilidades de segurança da informação e promover conscientização, educação e treinamento em segurança.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as lacunas de competências técnicas da área de segurança da informação necessárias para a atuação dos colaboradores da organização são identificadas e documentadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>realize diagnóstico periódico das lacunas de competências dos gestores e colaboradores de TIC e segurança da informação e estabeleça plano de tratamento, contemplando, conforme a necessidade, capacitação, realocação, provimento, apoio especializado, compartilhamento de estrutura ou contratação com transferência de conhecimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AV116</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>q2706ext[A]</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.
+ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3: definir papéis e responsabilidades de segurança da informação e promover conscientização, educação e treinamento em segurança.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que elabora plano de capacitação (plano de treinamento) visando o tratamento das lacunas de competência identificadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>realize diagnóstico periódico das lacunas de competências dos gestores e colaboradores de TIC e segurança da informação e estabeleça plano de tratamento, contemplando, conforme a necessidade, capacitação, realocação, provimento, apoio especializado, compartilhamento de estrutura ou contratação com transferência de conhecimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AV117</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>q2706ext[B]</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.
+ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3: definir papéis e responsabilidades de segurança da informação e promover conscientização, educação e treinamento em segurança.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que incentiva seus colaboradores e gestores a participar das ações de capacitação existentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>realize diagnóstico periódico das lacunas de competências dos gestores e colaboradores de TIC e segurança da informação e estabeleça plano de tratamento, contemplando, conforme a necessidade, capacitação, realocação, provimento, apoio especializado, compartilhamento de estrutura ou contratação com transferência de conhecimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>AV118</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>q2706ext[C]</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.03 - Manter habilidades e competências do pessoal: identificar, desenvolver e manter competências necessárias à execução das responsabilidades de TIC.
+ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2: definir responsabilidades e autoridades para segurança da informação e assegurar competências necessárias às funções atribuídas.
+ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3: definir papéis e responsabilidades de segurança da informação e promover conscientização, educação e treinamento em segurança.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que monitora a participação dos colaboradores e gestores nas ações de capacitação existentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>realize diagnóstico periódico das lacunas de competências dos gestores e colaboradores de TIC e segurança da informação e estabeleça plano de tratamento, contemplando, conforme a necessidade, capacitação, realocação, provimento, apoio especializado, compartilhamento de estrutura ou contratação com transferência de conhecimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AV119</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>q2703ext[B]</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.06 - Gerenciar pessoal contratado: controlar o uso de pessoal terceirizado ou externo, preservando responsabilização, supervisão e retenção de conhecimento.
+COBIT 2019, APO10.04 - Gerenciar risco de fornecedores: identificar e tratar riscos decorrentes de fornecedores, contratos e dependências externas relevantes para TIC.
+COBIT 2019, DSS01.02 - Gerenciar serviços de TI terceirizados: assegurar que serviços terceirizados sejam supervisionados, medidos e integrados aos controles da organização.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que definiu-se o quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação com base em critério(s) ou procedimento(s) técnico(s). Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AV120</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>q2703ext[C]</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.06 - Gerenciar pessoal contratado: controlar o uso de pessoal terceirizado ou externo, preservando responsabilização, supervisão e retenção de conhecimento.
+COBIT 2019, APO10.04 - Gerenciar risco de fornecedores: identificar e tratar riscos decorrentes de fornecedores, contratos e dependências externas relevantes para TIC.
+COBIT 2019, DSS01.02 - Gerenciar serviços de TI terceirizados: assegurar que serviços terceirizados sejam supervisionados, medidos e integrados aos controles da organização.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que definiu-se, de maneira documentada, um quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>AV121</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>q2801ext[E]</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.06 - Gerenciar pessoal contratado: controlar o uso de pessoal terceirizado ou externo, preservando responsabilização, supervisão e retenção de conhecimento.
+COBIT 2019, APO10.04 - Gerenciar risco de fornecedores: identificar e tratar riscos decorrentes de fornecedores, contratos e dependências externas relevantes para TIC.
+COBIT 2019, DSS01.02 - Gerenciar serviços de TI terceirizados: assegurar que serviços terceirizados sejam supervisionados, medidos e integrados aos controles da organização.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de trabalho para a gestão e fiscalização de contratos contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AV122</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>q2801ext[F]</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.06 - Gerenciar pessoal contratado: controlar o uso de pessoal terceirizado ou externo, preservando responsabilização, supervisão e retenção de conhecimento.
+COBIT 2019, APO10.04 - Gerenciar risco de fornecedores: identificar e tratar riscos decorrentes de fornecedores, contratos e dependências externas relevantes para TIC.
+COBIT 2019, DSS01.02 - Gerenciar serviços de TI terceirizados: assegurar que serviços terceirizados sejam supervisionados, medidos e integrados aos controles da organização.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que são disponibilizados artefatos padronizados para a gestão e fiscalização de contratos de TI, como modelos de plano de fiscalização, termos de recebimento, relatórios de acompanhamento, registros de ocorrências, avaliações de desempenho contratual ou documentos equivalentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AV123</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>q2804[A]</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO07.06 - Gerenciar pessoal contratado: controlar o uso de pessoal terceirizado ou externo, preservando responsabilização, supervisão e retenção de conhecimento.
+COBIT 2019, APO10.04 - Gerenciar risco de fornecedores: identificar e tratar riscos decorrentes de fornecedores, contratos e dependências externas relevantes para TIC.
+COBIT 2019, DSS01.02 - Gerenciar serviços de TI terceirizados: assegurar que serviços terceirizados sejam supervisionados, medidos e integrados aos controles da organização.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AV124</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>q2201ext[A]</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento do catálogo de serviços: manter fonte única de informações consistentes sobre serviços e ofertas de serviço, disponível para usuários e equipes de suporte.
+COBIT 2019, APO09.02 - Catalogar serviços facilitados por TI: definir, manter e comunicar catálogo de serviços, incluindo serviços prestados, características, requisitos e níveis de serviço esperados.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o catálogo contém as metas definidas para cada serviço (p. ex.: prazos de entrega, horários de serviço e de suporte, bem como pontos de contato para solicitação do serviço, envio de sugestões, esclarecimento de dúvidas e reporte de incidentes). Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>institua e mantenha atualizado catálogo de serviços de TIC, atentando-se, minimamente, em identificar os serviços efetivamente prestados, seus responsáveis, usuários, condições de acesso e informações necessárias ao atendimento das áreas demandantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AV125</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>q2201ext[B]</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento do catálogo de serviços: manter fonte única de informações consistentes sobre serviços e ofertas de serviço, disponível para usuários e equipes de suporte.
+COBIT 2019, APO09.02 - Catalogar serviços facilitados por TI: definir, manter e comunicar catálogo de serviços, incluindo serviços prestados, características, requisitos e níveis de serviço esperados.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o catálogo está atualizado e as informações que nele constam são compatíveis com os Acordos de Níveis de Serviço (ANS) estabelecidos pela área de tecnologia da informação e as áreas de negócio da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>institua e mantenha atualizado catálogo de serviços de TIC, atentando-se, minimamente, em identificar os serviços efetivamente prestados, seus responsáveis, usuários, condições de acesso e informações necessárias ao atendimento das áreas demandantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AV126</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>q2201ext[C]</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento do catálogo de serviços: manter fonte única de informações consistentes sobre serviços e ofertas de serviço, disponível para usuários e equipes de suporte.
+COBIT 2019, APO09.02 - Catalogar serviços facilitados por TI: definir, manter e comunicar catálogo de serviços, incluindo serviços prestados, características, requisitos e níveis de serviço esperados.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o catálogo é de fácil acesso e está amplamente disponível a seus usuários e às equipes de suporte. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>institua e mantenha atualizado catálogo de serviços de TIC, atentando-se, minimamente, em identificar os serviços efetivamente prestados, seus responsáveis, usuários, condições de acesso e informações necessárias ao atendimento das áreas demandantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AV127</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>q2201ext[D]</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO09.02 - Catalogar serviços facilitados por TI: definir, manter e comunicar catálogo de serviços, incluindo serviços prestados, características, requisitos e níveis de serviço esperados.
+ITIL 4, prática de gerenciamento de nível de serviço: definir, acordar, monitorar, avaliar e reportar metas e níveis de serviço alinhados às necessidades das áreas usuárias.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que são formalizados ANS contendo metas de nível de serviço acordadas com representantes das áreas de negócio clientes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Inexistência de ANS, metas mínimas de níveis de serviço para os principais serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>defina, pactue e monitore níveis mínimos de serviço ou metas de atendimento para os serviços de TIC mais relevantes, estabelecendo indicadores, responsáveis, periodicidade de medição e forma de comunicação dos resultados</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>AV128</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>q2201ext[E]</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>COBIT 2019, APO09.02 - Catalogar serviços facilitados por TI: definir, manter e comunicar catálogo de serviços, incluindo serviços prestados, características, requisitos e níveis de serviço esperados.
+ITIL 4, prática de gerenciamento de nível de serviço: definir, acordar, monitorar, avaliar e reportar metas e níveis de serviço alinhados às necessidades das áreas usuárias.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que a área de gestão de tecnologia da informação monitora continuamente o alcance dos níveis de serviço estabelecidos nos ANS. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Inexistência de ANS, metas mínimas de níveis de serviço para os principais serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>defina, pactue e monitore níveis mínimos de serviço ou metas de atendimento para os serviços de TIC mais relevantes, estabelecendo indicadores, responsáveis, periodicidade de medição e forma de comunicação dos resultados</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AV129</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>q2203ext[A]</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de ativos de TI: planejar e gerenciar o ciclo de vida dos ativos de TI, mantendo informações suficientes para apoiar controle, custo, risco, valor e tomada de decisão.
+ITIL 4, prática de gerenciamento de configuração de serviço: assegurar informações precisas e confiáveis sobre itens de configuração e seus relacionamentos com serviços, sistemas e infraestrutura.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>estabeleça e mantenha atualizado inventário de ativos de TIC, atentando-se, minimamente, em registrar equipamentos, servidores, sistemas, softwares, licenças, serviços em nuvem, componentes de infraestrutura, responsáveis e informações necessárias ao controle do ciclo de vida dos ativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>AV130</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>q2501ext[A]</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de ativos de TI: planejar e gerenciar o ciclo de vida dos ativos de TI, mantendo informações suficientes para apoiar controle, custo, risco, valor e tomada de decisão.
+ITIL 4, prática de gerenciamento de configuração de serviço: assegurar informações precisas e confiáveis sobre itens de configuração e seus relacionamentos com serviços, sistemas e infraestrutura.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que mantém um inventário dos ativos associados à informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>estabeleça e mantenha atualizado inventário de ativos de TIC, atentando-se, minimamente, em registrar equipamentos, servidores, sistemas, softwares, licenças, serviços em nuvem, componentes de infraestrutura, responsáveis e informações necessárias ao controle do ciclo de vida dos ativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>AV131</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>q2501ext[B]</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de ativos de TI: planejar e gerenciar o ciclo de vida dos ativos de TI, mantendo informações suficientes para apoiar controle, custo, risco, valor e tomada de decisão.
+ITIL 4, prática de gerenciamento de configuração de serviço: assegurar informações precisas e confiáveis sobre itens de configuração e seus relacionamentos com serviços, sistemas e infraestrutura.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que definiu responsabilidades pelos ativos associados à informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>estabeleça e mantenha atualizado inventário de ativos de TIC, atentando-se, minimamente, em registrar equipamentos, servidores, sistemas, softwares, licenças, serviços em nuvem, componentes de infraestrutura, responsáveis e informações necessárias ao controle do ciclo de vida dos ativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>AV132</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>q2504ext[A]</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de ativos de TI: planejar e gerenciar o ciclo de vida dos ativos de TI, mantendo informações suficientes para apoiar controle, custo, risco, valor e tomada de decisão.
+ITIL 4, prática de gerenciamento de configuração de serviço: assegurar informações precisas e confiáveis sobre itens de configuração e seus relacionamentos com serviços, sistemas e infraestrutura.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que gerencia (inventaria e controla) os dispositivos conectados em sua rede. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>estabeleça e mantenha atualizado inventário de ativos de TIC, atentando-se, minimamente, em registrar equipamentos, servidores, sistemas, softwares, licenças, serviços em nuvem, componentes de infraestrutura, responsáveis e informações necessárias ao controle do ciclo de vida dos ativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AV133</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>q2504ext[B]</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de ativos de TI: planejar e gerenciar o ciclo de vida dos ativos de TI, mantendo informações suficientes para apoiar controle, custo, risco, valor e tomada de decisão.
+ITIL 4, prática de gerenciamento de configuração de serviço: assegurar informações precisas e confiáveis sobre itens de configuração e seus relacionamentos com serviços, sistemas e infraestrutura.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>estabeleça e mantenha atualizado inventário de ativos de TIC, atentando-se, minimamente, em registrar equipamentos, servidores, sistemas, softwares, licenças, serviços em nuvem, componentes de infraestrutura, responsáveis e informações necessárias ao controle do ciclo de vida dos ativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>AV134</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>q2203ext[A]</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de configuração de serviço: assegurar informações precisas e confiáveis sobre itens de configuração e seus relacionamentos com serviços, sistemas e infraestrutura.
+COBIT 2019, BAI10.01 - Estabelecer e manter um modelo de configuração: definir escopo, granularidade, atributos, relacionamentos e responsáveis pela base de configuração.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade do processo de gestão de configuração.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>formalize e execute processo de gestão de configuração, atentando-se, minimamente, em manter base, ferramenta ou registro equivalente com os itens de configuração relevantes, seus responsáveis e os relacionamentos entre ativos, sistemas, infraestrutura e serviços, com atualização periódica e uso das informações no planejamento e acompanhamento de mudanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AV135</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>q2203ext[B]</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de configuração de serviço: assegurar informações precisas e confiáveis sobre itens de configuração e seus relacionamentos com serviços, sistemas e infraestrutura.
+COBIT 2019, BAI10.01 - Estabelecer e manter um modelo de configuração: definir escopo, granularidade, atributos, relacionamentos e responsáveis pela base de configuração.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que a base de dados de configurações é utilizada como insumo para o planejamento e o acompanhamento das mudanças. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade do processo de gestão de configuração.</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>formalize e execute processo de gestão de configuração, atentando-se, minimamente, em manter base, ferramenta ou registro equivalente com os itens de configuração relevantes, seus responsáveis e os relacionamentos entre ativos, sistemas, infraestrutura e serviços, com atualização periódica e uso das informações no planejamento e acompanhamento de mudanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>AV136</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>q2203ext[C]</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de configuração de serviço: assegurar informações precisas e confiáveis sobre itens de configuração e seus relacionamentos com serviços, sistemas e infraestrutura.
+COBIT 2019, BAI10.01 - Estabelecer e manter um modelo de configuração: definir escopo, granularidade, atributos, relacionamentos e responsáveis pela base de configuração.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de gestão de configuração e ativos está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades). Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade do processo de gestão de configuração.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>formalize e execute processo de gestão de configuração, atentando-se, minimamente, em manter base, ferramenta ou registro equivalente com os itens de configuração relevantes, seus responsáveis e os relacionamentos entre ativos, sistemas, infraestrutura e serviços, com atualização periódica e uso das informações no planejamento e acompanhamento de mudanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>AV137</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>q2204ext[A]</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de incidentes: minimizar o impacto negativo dos incidentes por meio da restauração tempestiva da operação normal dos serviços e do registro rastreável do tratamento realizado.
+COBIT 2019, DSS02.02, DSS02.04 e DSS02.07 - Requisições de serviço e incidentes gerenciados: registrar, classificar, priorizar, investigar, diagnosticar, resolver, acompanhar e reportar incidentes e requisições de serviço.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que definiu regras para a priorização e o escalamento de incidentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>formalize e execute processo de gestão de incidentes de TIC, atentando-se, minimamente, em definir papéis, responsabilidades, critérios de priorização e escalamento, tratamento de incidentes de serviços e de segurança da informação, registro sistemático e rastreável das ocorrências e análise posterior dos incidentes relevantes ou recorrentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AV138</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>q2204ext[B]</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de incidentes: minimizar o impacto negativo dos incidentes por meio da restauração tempestiva da operação normal dos serviços e do registro rastreável do tratamento realizado.
+COBIT 2019, DSS02.02, DSS02.04 e DSS02.07 - Requisições de serviço e incidentes gerenciados: registrar, classificar, priorizar, investigar, diagnosticar, resolver, acompanhar e reportar incidentes e requisições de serviço.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que a resolução de incidentes considera os níveis de serviços especificados em acordos com as áreas clientes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>formalize e execute processo de gestão de incidentes de TIC, atentando-se, minimamente, em definir papéis, responsabilidades, critérios de priorização e escalamento, tratamento de incidentes de serviços e de segurança da informação, registro sistemático e rastreável das ocorrências e análise posterior dos incidentes relevantes ou recorrentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AV139</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>q2204ext[C]</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de incidentes: minimizar o impacto negativo dos incidentes por meio da restauração tempestiva da operação normal dos serviços e do registro rastreável do tratamento realizado.
+COBIT 2019, DSS02.02, DSS02.04 e DSS02.07 - Requisições de serviço e incidentes gerenciados: registrar, classificar, priorizar, investigar, diagnosticar, resolver, acompanhar e reportar incidentes e requisições de serviço.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que há base(s) de conhecimento que registra(m) erros conhecidos e problemas, de modo a tornar eficiente e efetiva a resolução de incidentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>formalize e execute processo de gestão de incidentes de TIC, atentando-se, minimamente, em definir papéis, responsabilidades, critérios de priorização e escalamento, tratamento de incidentes de serviços e de segurança da informação, registro sistemático e rastreável das ocorrências e análise posterior dos incidentes relevantes ou recorrentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AV140</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>q2204ext[D]</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de incidentes: minimizar o impacto negativo dos incidentes por meio da restauração tempestiva da operação normal dos serviços e do registro rastreável do tratamento realizado.
+COBIT 2019, DSS02.02, DSS02.04 e DSS02.07 - Requisições de serviço e incidentes gerenciados: registrar, classificar, priorizar, investigar, diagnosticar, resolver, acompanhar e reportar incidentes e requisições de serviço.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o(s) processo(s) de gestão de incidentes está(ão) formalizado(s) (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades). Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>formalize e execute processo de gestão de incidentes de TIC, atentando-se, minimamente, em definir papéis, responsabilidades, critérios de priorização e escalamento, tratamento de incidentes de serviços e de segurança da informação, registro sistemático e rastreável das ocorrências e análise posterior dos incidentes relevantes ou recorrentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>AV141</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>q2204ext[E]</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de incidentes: minimizar o impacto negativo dos incidentes por meio da restauração tempestiva da operação normal dos serviços e do registro rastreável do tratamento realizado.
+COBIT 2019, DSS02.02, DSS02.04 e DSS02.07 - Requisições de serviço e incidentes gerenciados: registrar, classificar, priorizar, investigar, diagnosticar, resolver, acompanhar e reportar incidentes e requisições de serviço.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que definiu procedimentos e responsabilidades quanto à notificação e ao tratamento das notificações de incidentes de segurança da informação, bem como quanto à adoção de ações emergenciais, diretrizes para escalamento e comunicação interna e externa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>formalize e execute processo de gestão de incidentes de TIC, atentando-se, minimamente, em definir papéis, responsabilidades, critérios de priorização e escalamento, tratamento de incidentes de serviços e de segurança da informação, registro sistemático e rastreável das ocorrências e análise posterior dos incidentes relevantes ou recorrentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AV142</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>q2204ext[F]</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>ITIL 4, prática de gerenciamento de incidentes: minimizar o impacto negativo dos incidentes por meio da restauração tempestiva da operação normal dos serviços e do registro rastreável do tratamento realizado.
+COBIT 2019, DSS02.02, DSS02.04 e DSS02.07 - Requisições de serviço e incidentes gerenciados: registrar, classificar, priorizar, investigar, diagnosticar, resolver, acompanhar e reportar incidentes e requisições de serviço.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que definiu procedimentos e responsabilidades quanto à análise dos incidentes, identificação de causas raízes e planejamento e implementação de ações corretivas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>formalize e execute processo de gestão de incidentes de TIC, atentando-se, minimamente, em definir papéis, responsabilidades, critérios de priorização e escalamento, tratamento de incidentes de serviços e de segurança da informação, registro sistemático e rastreável das ocorrências e análise posterior dos incidentes relevantes ou recorrentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AV143</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>q2801ext[A]</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Art. 11, parágrafo único, da Lei 14.133/2021: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos.
+Art. 19, inciso IV, da Lei 14.133/2021: instituição de modelos de minutas de editais, termos de referência, contratos padronizados e demais documentos.
+COBIT 2019, APO01.09 - Definir e comunicar políticas e procedimentos: manter políticas, procedimentos e orientações para direcionar processos de gestão de TIC.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de trabalho para o planejamento das contratações de TI contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AV144</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>q2801ext[C]</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Art. 11, parágrafo único, da Lei 14.133/2021: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos.
+Art. 19, inciso IV, da Lei 14.133/2021: instituição de modelos de minutas de editais, termos de referência, contratos padronizados e demais documentos.
+COBIT 2019, APO01.09 - Definir e comunicar políticas e procedimentos: manter políticas, procedimentos e orientações para direcionar processos de gestão de TIC.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de trabalho para a seleção de fornecedores contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AV145</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>q2801ext[D]</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Art. 11, parágrafo único, da Lei 14.133/2021: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos.
+Art. 19, inciso IV, da Lei 14.133/2021: instituição de modelos de minutas de editais, termos de referência, contratos padronizados e demais documentos.
+COBIT 2019, APO01.09 - Definir e comunicar políticas e procedimentos: manter políticas, procedimentos e orientações para direcionar processos de gestão de TIC.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que são disponibilizados artefatos padronizados para a fase de seleção de fornecedores, como minutas, checklists, modelos de edital, pareceres, critérios de julgamento ou documentos equivalentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AV146</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>q2801ext[E]</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Art. 11, parágrafo único, da Lei 14.133/2021: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos.
+Art. 19, inciso IV, da Lei 14.133/2021: instituição de modelos de minutas de editais, termos de referência, contratos padronizados e demais documentos.
+COBIT 2019, APO01.09 - Definir e comunicar políticas e procedimentos: manter políticas, procedimentos e orientações para direcionar processos de gestão de TIC.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de trabalho para a gestão e fiscalização de contratos contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AV147</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>q2801ext[G]</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Art. 11, parágrafo único, da Lei 14.133/2021: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos.
+Art. 19, inciso IV, da Lei 14.133/2021: instituição de modelos de minutas de editais, termos de referência, contratos padronizados e demais documentos.
+COBIT 2019, APO01.09 - Definir e comunicar políticas e procedimentos: manter políticas, procedimentos e orientações para direcionar processos de gestão de TIC.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que os processos de trabalho e os artefatos padronizados estão aderentes às normas legais e infralegais que regem as contratações públicas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AV148</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>q2804[A]</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Art. 11, parágrafo único, da Lei 14.133/2021: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos.
+COBIT 2019, BAI02.04 - Obter aprovação dos requisitos da solução: obter aprovação formal dos requisitos funcionais, técnicos, de segurança e de conformidade antes de prosseguir com a solução.
+COBIT 2019, APO01.05 - Estabelecer papéis e responsabilidades: definir e comunicar papéis e responsabilidades relacionados à informação e à tecnologia.
+Instrução Normativa SGD/ME nº 94, de 23 de dezembro de 2022, art. 1º, § 1º: como referência de boa prática, a aplicação de ritos formais de contratação de TIC pode ser facultada para contratações diretas por dispensa em razão do valor (inciso II do art. 75 da Lei nº 14.133/2021), indicando a possibilidade de fluxos simplificados para aquisições de baixa complexidade ou valor.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem análise prévia e aprovação técnica obrigatória da área de TIC.</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>estabeleça a submissão das contratações de TIC à análise prévia e à aprovação técnica da área de TIC, inclusive quando demandadas por outras áreas, de modo a verificar a compatibilidade da solução com os padrões tecnológicos, os requisitos institucionais, a segurança da informação e a arquitetura existente, facultando a adoção de fluxos simplificados ou a dispensa de parecer detalhado para contratações diretas por dispensa em razão do valor (baixo valor) ou de baixa complexidade técnica, mediante critérios objetivos ou catálogos de soluções padronizadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AV149</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>q2102ext[C]</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Art. 11, parágrafo único, da Lei 14.133/2021: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos.
+Art. 18, caput e §1º, incisos I, IV, V, VIII, IX, X e XIII, da Lei 14.133/2021: fase preparatória caracterizada pelo planejamento, compatibilização com o plano de contratações anual e elementos mínimos do estudo técnico preliminar.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o plano de TI fundamenta a proposta orçamentária da área de TI e o plano de contratações. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem aderência ao plano de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>integre as contratações de TIC ao planejamento de TIC, ao plano de contratações e à proposta orçamentária, atentando-se, minimamente, em registrar a necessidade atendida, a prioridade, a disponibilidade de recursos e a justificativa das situações excepcionais</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>AV150</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>q2802ext[C]</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Art. 11, parágrafo único, da Lei 14.133/2021: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos.
+Art. 18, caput e §1º, incisos I, IV, V, VIII, IX, X e XIII, da Lei 14.133/2021: fase preparatória caracterizada pelo planejamento, compatibilização com o plano de contratações anual e elementos mínimos do estudo técnico preliminar.</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que na elaboração do PCA são considerados os demais instrumentos de planejamento da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem aderência ao plano de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>integre as contratações de TIC ao planejamento de TIC, ao plano de contratações e à proposta orçamentária, atentando-se, minimamente, em registrar a necessidade atendida, a prioridade, a disponibilidade de recursos e a justificativa das situações excepcionais</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>AV151</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>avaliacao_evidencias_ajustes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>q2802ext[D]</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Art. 11, parágrafo único, da Lei 14.133/2021: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos.
+Art. 18, caput e §1º, incisos I, IV, V, VIII, IX, X e XIII, da Lei 14.133/2021: fase preparatória caracterizada pelo planejamento, compatibilização com o plano de contratações anual e elementos mínimos do estudo técnico preliminar.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Evidência insuficiente para comprovar a prática declarada de que o PCA fundamenta a proposta orçamentária da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem aderência ao plano de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>integre as contratações de TIC ao planejamento de TIC, ao plano de contratações e à proposta orçamentária, atentando-se, minimamente, em registrar a necessidade atendida, a prioridade, a disponibilidade de recursos e a justificativa das situações excepcionais</t>
         </is>
       </c>
     </row>
